--- a/artfynd/A 11534-2025 artfynd.xlsx
+++ b/artfynd/A 11534-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119238741</v>
+        <v>119239166</v>
       </c>
       <c r="B2" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>702515</v>
+        <v>702464</v>
       </c>
       <c r="R2" t="n">
-        <v>7277033</v>
+        <v>7277057</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -791,37 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119239124</v>
+        <v>119239115</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -910,12 +900,7 @@
         <v>119238697</v>
       </c>
       <c r="B4" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,15 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119239115</v>
+        <v>119238771</v>
       </c>
       <c r="B5" t="n">
-        <v>91826</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +1019,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1072,13 +1052,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>702464</v>
+        <v>702511</v>
       </c>
       <c r="R5" t="n">
-        <v>7277057</v>
+        <v>7277045</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1139,15 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119239166</v>
+        <v>119239124</v>
       </c>
       <c r="B6" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1130,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1255,15 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119238771</v>
+        <v>119238741</v>
       </c>
       <c r="B7" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1304,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>702511</v>
+        <v>702515</v>
       </c>
       <c r="R7" t="n">
-        <v>7277045</v>
+        <v>7277033</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1368,6 +1338,117 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>119238662</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92841</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vierakejávrrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>702517</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7276954</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>John-Olof Halvarsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>John-Olof Halvarsson, Ingunn Woldmo</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
